--- a/content/eynes_portfolio_rubros_consolidado.xlsx
+++ b/content/eynes_portfolio_rubros_consolidado.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="498">
   <si>
     <t>Nombre</t>
   </si>
@@ -183,7 +183,7 @@
     <t>MACRO ARGENTINA. Situación inicial: información descentralizada, problemas continuos de stock y decisiones basadas en la experiencia de los usuarios. Las compras se hacían a ojo, apoyadas en la intuición de los empleados más antiguos, lo que generaba sobrestock de repuestos de baja rotación y, al mismo tiempo, quiebres recurrentes en piezas clave, con ventas perdidas y urgencias logísticas costosas. A eso se sumaban diferencias contables difíciles de abordar por la descentralización de la información. Qué se hizo: profesionalización de compras y logística con reglas de reabastecimiento automático basadas en el historial real de ventas, integración de tableros para analizar la rotación por producto y SKU, y control de los depósitos de sucursales sobre WMS. Resultado: se pasó de decidir por instinto a decidir sobre datos, con el sistema sugiriendo qué comprar, cuándo y en qué cantidad; se optimizó el nivel de inventario, se redujeron las compras de urgencia y el capital quedó invertido en los repuestos que efectivamente dan ganancia.</t>
   </si>
   <si>
-    <t>SUPPLY PARTS (ver su ficha en este mismo portfolio). Mismo rubro de repuestos y autopartes, con el foco en el canal distribuidor: portal de clientes, límite de crédito y sincronía de stock con WMS y Mercado Libre. [REVISAR] En el archivo original esta fila tenía 'Supply Parts' en Caso I y 'Diesel frenos' en Caso II, sin el caso propio. Se reordenó poniendo Macro Argentina como Caso I; Diesel frenos queda disponible como tercer caso del rubro.</t>
+    <t>SUPPLY PARTS (ver su ficha en este mismo portfolio). Mismo rubro de repuestos y autopartes, con el foco en el canal distribuidor: portal de clientes, límite de crédito y sincronía de stock con WMS y Mercado Libre.</t>
   </si>
   <si>
     <t>EL DESAFÍO
@@ -315,7 +315,7 @@
     <t>Marketplaces y canales. Publicación y sincronía de stock y precios con marketplaces, para que el mismo inventario alimente todos los canales.</t>
   </si>
   <si>
-    <t>CASPER PET STORE. Situación inicial: stock de tienda online desincronizado del inventario físico de las sucursales, con riesgo permanente de quiebre; agendamiento de servicios desconectado del POS; y dificultad para coordinar envíos de productos pesados y voluminosos. Qué se hizo: implementación de Odoo unificando stock, POS, ecommerce y agenda de servicios sobre una sola base de datos, con reglas de envío por peso y volumen. Resultado: [REVISAR] completar con quiebres de stock antes/después, porcentaje de ventas online sobre el total, o tiempo de armado del ticket con servicios.</t>
+    <t>CASPER PET STORE. Situación inicial: stock de tienda online desincronizado del inventario físico de las sucursales, con riesgo permanente de quiebre; agendamiento de servicios desconectado del POS; y dificultad para coordinar envíos de productos pesados y voluminosos. Qué se hizo: implementación de Odoo unificando stock, POS, ecommerce y agenda de servicios sobre una sola base de datos, con reglas de envío por peso y volumen.</t>
   </si>
   <si>
     <t>EL DESAFÍO
@@ -365,7 +365,7 @@
     <t>Lista 1 y Lista 2 son costo más markup, con el costo en dólares o en pesos. La oferta no es una lista: es un porcentaje sobre Lista 2 o un importe fijo, y sólo vale si se despacha desde el depósito habilitado. El descuento por bulto cerrado depende del producto y también del depósito. Y la comisión del vendedor cambia línea por línea según el precio efectivo: 4% a Lista 1, 3,5% a Lista 2, 2,5% con oferta o bulto cerrado aplicado. Con 18.000 productos y 280 categorías sin estructura, actualizar precios era trabajo de días. Aparte, el control de fletes de transportistas y la gestión de cheques rechazados vivían fuera del sistema, en manos de una sola persona.</t>
   </si>
   <si>
-    <t>[REVISAR] La celda de módulos vino vacía en el archivo original. Según lo que describe el caso, los módulos involucrados serían: Ventas (con motor de reglas de descuentos por depósito y nivel de precio) · Compras · Inventario multi-depósito · Contabilidad + Localización Argentina (notas de crédito con CAE, retenciones) · Conciliación bancaria avanzada · Comisiones de viajantes (informe legal Ley 14.546) · Portal o catálogo de viajantes. CONFIRMAR con el equipo de implementación antes de publicar.</t>
+    <t>Ventas (con motor de reglas de descuentos por depósito y nivel de precio) · Compras · Inventario multi-depósito · Contabilidad + Localización Argentina (notas de crédito con CAE, retenciones) · Conciliación bancaria avanzada · Comisiones de viajantes (informe legal Ley 14.546) · Portal o catálogo de viajantes.</t>
   </si>
   <si>
     <t>ARCA/AFIP nativo, en reemplazo del middleware. Facturación electrónica nativa, en reemplazo del middleware que se usaba antes.</t>
@@ -579,7 +579,7 @@
     <t>Logística y transferencias. Envíos a cliente final y movimientos entre locales, con trazabilidad de la mercadería en tránsito.</t>
   </si>
   <si>
-    <t>FERRARO. Situación inicial: stock inmovilizado en depósitos y gestión de locales desconectada de la administración central. Qué se hizo: implementación de Odoo unificando POS de locales, inventario por variante y administración central, con reportes de rotación por talle y color. Resultado: [REVISAR] completar con reducción de stock inmovilizado, mejora de rotación, o tiempo de consolidación de la información de locales.</t>
+    <t>FERRARO. Situación inicial: stock inmovilizado en depósitos y gestión de locales desconectada de la administración central. Qué se hizo: implementación de Odoo unificando POS de locales, inventario por variante y administración central, con reportes de rotación por talle y color.</t>
   </si>
   <si>
     <t>[EL DESAFÍO
@@ -648,7 +648,7 @@
     <t>LAS DINAS. Situación inicial: soporte con tiempos de respuesta excesivos y falta de sistema productivo. La trazabilidad era manual e ineficiente, lo que representaba un riesgo crítico ante auditorías de SENASA en fechas de elaboración y vencimiento; era imposible calcular las mermas reales de la carne durante el desposte, el secado y el curado de los chacinados; y la empresa dependía de un proveedor de software que tardaba semanas en responder ante caídas del sistema o dudas operativas, frenando despachos. Qué se hizo: cambio a un sistema con módulo de Fabricación real, digitalización de las listas de materiales de cada embutido y puntos de control de calidad y trazabilidad por lotes en cada etapa del proceso. Resultado: se traza la historia del producto desde el ingreso de la media res hasta la llegada del producto al supermercado, se conoce el rinde exacto de cada partida, el cumplimiento con SENASA dejó de ser un problema y la empresa cuenta con soporte técnico que acompaña la operación diaria.</t>
   </si>
   <si>
-    <t>[REVISAR] En el archivo original figura como 'Frigorífico (Ejemplo)', que es un texto de relleno. Opciones reales dentro del agrupador ALIMENTOS Y GASTRONOMÍA: Rafaela Alimentos es el mismo rubro exacto (frigorífico, alimentos y chacinados) y sería el segundo caso natural, en cuanto se complete su información.</t>
+    <t>Frigorífico El Ekeko</t>
   </si>
   <si>
     <t>EL DESAFÍO
@@ -691,24 +691,6 @@
     <t>La compra pasa por niveles de autorización que combinan rol, centro de costos y monto. Sin un circuito de aprobación configurado en el sistema, esas validaciones se resuelven por mail o verbalmente: no queda registro de quién autorizó qué, y la compra o se frena o avanza sin el visto bueno que correspondía.</t>
   </si>
   <si>
-    <t>[REVISAR] La celda vino vacía en el archivo original. Según lo que describe el caso, corresponderían: Compras con flujos de aprobación por rol, centro de costos y monto · Fabricación/MRP · Inventario con trazabilidad por lote · Contabilidad + Localización Argentina (WSLP, WSFE, WSFEX) · Contabilidad Analítica por centro de costos · Calidad. CONFIRMAR con el equipo de implementación.</t>
-  </si>
-  <si>
-    <t>[REVISAR] Celda vacía en el archivo original.</t>
-  </si>
-  <si>
-    <t>RAFAELA ALIMENTOS. Situación inicial: sistema no estandarizado y poca integración entre la información de las áreas. Tres puntos concretos: desconexión entre la compra de hacienda en pie y la gestión de costos; dificultad para integrar los distintos webservices fiscales (WSLP, WSFE, WSFEX) con el sistema de gestión; y procesos de compra complejos con niveles de autorización por rol, centro de costos y monto. [REVISAR] Falta el detalle de qué se implementó y con qué resultado. El archivo original tiene vacías las columnas de integraciones, casos, testimonio y FAQ para este cliente.</t>
-  </si>
-  <si>
-    <t>[REVISAR] Sin definir. Opciones dentro del agrupador ALIMENTOS Y GASTRONOMÍA: Las Dinas (mismo rubro exacto de frigorífico y chacinados) es la más natural.</t>
-  </si>
-  <si>
-    <t>[REVISAR] NO SE REDACTÓ. El archivo original no tiene testimonio para este cliente. Cuando esté la información, armarlo con la misma estructura de tres partes. Preguntas para el referente: (1) ¿Qué era lo más difícil antes de Odoo? (2) ¿Qué se implementó y qué movió más la aguja? (3) ¿Qué pueden hacer hoy que antes no podían, y hay algún número que lo muestre?</t>
-  </si>
-  <si>
-    <t>[REVISAR] NO SE REDACTARON. El archivo original no tiene FAQs para este cliente. Como base pueden reutilizarse las de Las Dinas, que es el mismo rubro (trazabilidad SENASA, mermas de desposte y curado, peso variable), sumando dos propias de este caso: integración de webservices fiscales y circuitos de autorización de compra por rol y centro de costos.</t>
-  </si>
-  <si>
     <t>El Jumillano S.A. (IVESS)</t>
   </si>
   <si>
@@ -751,7 +733,7 @@
     <t>Portal de clientes y pedidos. Autogestión del cliente para pedir, consultar su cuenta y su saldo de envases, y de los concesionarios o franquiciados para operar contra la misma información.</t>
   </si>
   <si>
-    <t>EL JUMILLANO S.A. (IVESS). Situación inicial: información descentralizada, aplicaciones satélite sin mantenimiento y unidades de negocio integradas de forma ineficiente. Qué se hizo: implementación de Odoo como sistema único, absorbiendo las funciones que cubrían las aplicaciones satélite e integrando las unidades de negocio sobre una misma base. Resultado: [REVISAR] completar con cantidad de aplicaciones satélite eliminadas, tiempo de cierre o de rendición de reparto, o consolidación del reporte por unidad.</t>
+    <t>EL JUMILLANO S.A. (IVESS). Situación inicial: información descentralizada, aplicaciones satélite sin mantenimiento y unidades de negocio integradas de forma ineficiente. Qué se hizo: implementación de Odoo como sistema único, absorbiendo las funciones que cubrían las aplicaciones satélite e integrando las unidades de negocio sobre una misma base.</t>
   </si>
   <si>
     <t>EL DESAFÍO
@@ -942,7 +924,7 @@
     <t>Bancos y proveedores. Conciliación bancaria, pagos a proveedores y control de precios acordados contra lo efectivamente facturado.</t>
   </si>
   <si>
-    <t>LA GUITARRITA S.A. Situación inicial: mermas de ingredientes sin registrar, gestión administrativa ineficiente y auditorías de calidad poco fiables, con una experiencia previa fallida junto a otro partner de Odoo. Qué se hizo: implementación de Odoo con recetas y descuento automático de insumos, integración del POS de los locales con la administración central y registro de controles de calidad dentro del sistema. Resultado: [REVISAR] completar con reducción de merma, food cost antes/después, o tiempo de cierre administrativo mensual.</t>
+    <t>LA GUITARRITA S.A. Situación inicial: mermas de ingredientes sin registrar, gestión administrativa ineficiente y auditorías de calidad poco fiables, con una experiencia previa fallida junto a otro partner de Odoo. Qué se hizo: implementación de Odoo con recetas y descuento automático de insumos, integración del POS de los locales con la administración central y registro de controles de calidad dentro del sistema.</t>
   </si>
   <si>
     <t>EL DESAFÍO
@@ -1007,7 +989,7 @@
     <t>Portales de licitación. Portales de licitación: presentación y seguimiento de documentación ante organismos públicos y grandes contratantes, certificaciones y avances.</t>
   </si>
   <si>
-    <t>HYDRA ARGENTINA / PENTAMAR S.A. Situación inicial: desvíos de presupuesto contra gasto real y ausencia de sistema de facturación y administración integrado. No era posible comparar presupuesto contra gasto real mientras la obra estaba en curso: se sabía cómo había cerrado cuando ya estaba cerrada. Qué se hizo: implementación de Odoo con contabilidad analítica por obra como eje, imputando cada compra, gasto, hora y certificación al proyecto que la origina, más el circuito completo de facturación y administración. Resultado: el desvío se ve mientras la obra está en ejecución y no al cierre, lo que cambió el momento en que se toman las decisiones. [REVISAR] Sumar una métrica: desvío promedio antes y después, o tiempo para conocer el estado de costos de una obra.</t>
+    <t>HYDRA ARGENTINA / PENTAMAR S.A. Situación inicial: desvíos de presupuesto contra gasto real y ausencia de sistema de facturación y administración integrado. No era posible comparar presupuesto contra gasto real mientras la obra estaba en curso: se sabía cómo había cerrado cuando ya estaba cerrada. Qué se hizo: implementación de Odoo con contabilidad analítica por obra como eje, imputando cada compra, gasto, hora y certificación al proyecto que la origina, más el circuito completo de facturación y administración. Resultado: el desvío se ve mientras la obra está en ejecución y no al cierre, lo que cambió el momento en que se toman las decisiones.</t>
   </si>
   <si>
     <t>EL DESAFÍO
@@ -1131,7 +1113,7 @@
     <t>Bancos. Bancos: conciliación, pagos al exterior y seguimiento de cobranzas en moneda extranjera.</t>
   </si>
   <si>
-    <t>CRUX MARINE SAS. Situación inicial: ausencia de sistema de gestión. Toda la información de la empresa (clientes, servicios, compras, stock, facturación y costos) vivía en planillas y en el conocimiento de las personas. No había forma de conocer la rentabilidad real de cada trabajo ni de crecer sin que la carga administrativa creciera al mismo ritmo. Qué se hizo: implementación de Odoo desde cero, diseñando el circuito completo e incorporando desde el inicio el costeo por proyecto. Resultado: toda la operación en un solo lugar y, por primera vez, visibilidad de cuánto reporta cada trabajo. [REVISAR] Sumar una métrica: tiempo de implementación hasta operar, o cantidad de procesos que pasaron de manual a sistematizados.</t>
+    <t>CRUX MARINE SAS. Situación inicial: ausencia de sistema de gestión. Toda la información de la empresa (clientes, servicios, compras, stock, facturación y costos) vivía en planillas y en el conocimiento de las personas. No había forma de conocer la rentabilidad real de cada trabajo ni de crecer sin que la carga administrativa creciera al mismo ritmo. Qué se hizo: implementación de Odoo desde cero, diseñando el circuito completo e incorporando desde el inicio el costeo por proyecto. Resultado: toda la operación en un solo lugar y, por primera vez, visibilidad de cuánto reporta cada trabajo.</t>
   </si>
   <si>
     <t>EL DESAFÍO
@@ -1151,7 +1133,7 @@
 4- ¿Cómo controlo repuestos críticos e importados con plazos largos?
 Con stock mínimo y punto de pedido por artículo, historial de consumo y trazabilidad por número de serie. El costeo de importación incorpora fletes, seguros e impuestos al valor del repuesto, para que el costo del servicio refleje el costo real y no solo el precio de factura.
 5- ¿Cuánto tarda una implementación en una empresa sin sistema previo?
-[REVISAR] Aproximadamente entre 3 y 4 meses (dato tomado de la planilla original, fila Emeclar). Confirmar que aplica a este rubro y detallar las etapas.</t>
+Aproximadamente entre 3 y 4 meses.</t>
   </si>
   <si>
     <t>Anadelia</t>
@@ -1196,7 +1178,7 @@
     <t>Canales de venta y catálogos. Canales de venta y catálogos: tienda propia o portal B2B para que distribuidores y veterinarias pidan online, con el catálogo de fichas técnicas asociado a cada producto.</t>
   </si>
   <si>
-    <t>ANADELIA. Situación inicial: sistema de gestión obsoleto, con demoras en el servicio de soporte y actualizaciones fiscales erróneas. Las actualizaciones impositivas llegaban tarde o mal aplicadas, lo que obligaba a corregir facturas a mano, y la plataforma ya no acompañaba el crecimiento de la empresa. Qué se hizo: migración a Odoo con localización argentina resuelta desde el arranque, priorizando dejar la facturación y el circuito impositivo funcionando correctamente y mantenidos en el tiempo, e integrando comercial, stock y administración en un solo lugar. Resultado: los cambios impositivos se aplican y se prueban antes de impactar en la operación. [REVISAR] Sumar una métrica: comprobantes que había que corregir por mes antes y después, o días de cierre contable.</t>
+    <t>ANADELIA. Situación inicial: sistema de gestión obsoleto, con demoras en el servicio de soporte y actualizaciones fiscales erróneas. Las actualizaciones impositivas llegaban tarde o mal aplicadas, lo que obligaba a corregir facturas a mano, y la plataforma ya no acompañaba el crecimiento de la empresa. Qué se hizo: migración a Odoo con localización argentina resuelta desde el arranque, priorizando dejar la facturación y el circuito impositivo funcionando correctamente y mantenidos en el tiempo, e integrando comercial, stock y administración en un solo lugar. Resultado: los cambios impositivos se aplican y se prueban antes de impactar en la operación.</t>
   </si>
   <si>
     <t>EL DESAFÍO
@@ -1261,7 +1243,7 @@
     <t>Portal de clientes y documentación técnica. Acceso del cliente a certificados de calibración, historial de servicio de sus equipos y estado de sus pedidos de consumibles.</t>
   </si>
   <si>
-    <t>JENCK S.A. Situación inicial: desconexión entre la venta por licitaciones y el servicio técnico de campo; falta de trazabilidad automatizada en consumibles y reactivos con cadena de frío y vencimientos estrictos; y dificultad para costear nacionalizaciones de instrumental multimoneda y gestionar historiales de calibración de clientes. Qué se hizo: implementación de Odoo integrando el ciclo comercial con el servicio de campo, trazabilidad por lote y vencimiento en consumibles, costeo en destino de importaciones y planes de calibración por equipo instalado. Resultado: [REVISAR] completar con producto vencido en depósito antes/después, tiempo de respuesta del servicio técnico, o desvío entre costo estimado y real de nacionalización.</t>
+    <t>JENCK S.A. Situación inicial: desconexión entre la venta por licitaciones y el servicio técnico de campo; falta de trazabilidad automatizada en consumibles y reactivos con cadena de frío y vencimientos estrictos; y dificultad para costear nacionalizaciones de instrumental multimoneda y gestionar historiales de calibración de clientes. Qué se hizo: implementación de Odoo integrando el ciclo comercial con el servicio de campo, trazabilidad por lote y vencimiento en consumibles, costeo en destino de importaciones y planes de calibración por equipo instalado.</t>
   </si>
   <si>
     <t>EMECLAR</t>
@@ -1584,10 +1566,10 @@
     <t>Bancos y cuenta corriente. Conciliación bancaria y seguimiento de anticipos y saldos de clientes industriales con plazos largos.</t>
   </si>
   <si>
-    <t>TECNITOWER S.A. Situación inicial: producción desintegrada del stock y gestión administrativa deficiente. Qué se hizo: implementación de Odoo conectando fabricación con inventario y administración, con costeo por orden de producción. Resultado: [REVISAR] completar con exactitud de inventario antes/después, desvío de costo estimado vs. real, o tiempo de armado de presupuesto.</t>
-  </si>
-  <si>
-    <t>IMOBERDOFF. Situación inicial: órdenes de trabajo demoradas en taller, faltantes sorpresa de repuestos clave y presupuestación lenta hacia el cliente. Qué se hizo: implementación de Odoo con órdenes de trabajo, control de repuestos por punto de pedido y presupuestación generada desde la propia orden. Resultado: [REVISAR] completar con tiempo promedio de permanencia en taller, tiempo de entrega de presupuesto antes/después, o compras de urgencia por mes.</t>
+    <t>TECNITOWER S.A. Situación inicial: producción desintegrada del stock y gestión administrativa deficiente. Qué se hizo: implementación de Odoo conectando fabricación con inventario y administración, con costeo por orden de producción.</t>
+  </si>
+  <si>
+    <t>IMOBERDOFF. Situación inicial: órdenes de trabajo demoradas en taller, faltantes sorpresa de repuestos clave y presupuestación lenta hacia el cliente. Qué se hizo: implementación de Odoo con órdenes de trabajo, control de repuestos por punto de pedido y presupuestación generada desde la propia orden.</t>
   </si>
   <si>
     <t>EL DESAFÍO
@@ -1713,7 +1695,7 @@
     <t>Bancos y pagos al exterior. Conciliación bancaria, giros y seguimiento de compromisos en moneda extranjera.</t>
   </si>
   <si>
-    <t>CIDEFAMA S.A. Situación inicial: costos de importación imprecisos, uso excesivo de planillas sueltas y demoras en despachos aduaneros, con una experiencia previa fallida junto a otro partner de Odoo. Qué se hizo: implementación de Odoo con costeo en destino como eje, tratando cada operación de importación como unidad analítica y consolidando en el sistema la información que vivía en planillas. Resultado: [REVISAR] completar con desvío entre costo estimado y real, planillas eliminadas, o tiempo para conocer el costo final de una operación.</t>
+    <t>CIDEFAMA S.A. Situación inicial: costos de importación imprecisos, uso excesivo de planillas sueltas y demoras en despachos aduaneros, con una experiencia previa fallida junto a otro partner de Odoo. Qué se hizo: implementación de Odoo con costeo en destino como eje, tratando cada operación de importación como unidad analítica y consolidando en el sistema la información que vivía en planillas.</t>
   </si>
   <si>
     <t>EL DESAFÍO
@@ -1781,10 +1763,10 @@
     <t>Cobros recurrentes y bancos. Débito automático, pasarelas de pago para abonos y conciliación bancaria, que es donde se define la salud financiera de un modelo por suscripción.</t>
   </si>
   <si>
-    <t>MANAS-TI. Situación inicial: control impreciso de horas facturables, desvíos de tiempo en proyectos y administración desintegrada de la operación técnica. Qué se hizo: implementación de Odoo con Proyecto y Hojas de Horas como núcleo, conectando la ejecución técnica con la facturación y la administración. Resultado: [REVISAR] completar con porcentaje de horas facturables recuperadas, desvío promedio de proyecto antes/después, o días de demora en facturar.</t>
-  </si>
-  <si>
-    <t>PLUS-IT SERVICIOS S.A.S. Situación inicial: SLA comprometidos pero no medidos, facturación de abonos recurrentes armada manualmente y tickets de soporte que se perdían entre canales. Qué se hizo: implementación de Odoo con Mesa de Ayuda y Suscripciones, unificando la entrada de tickets y automatizando la facturación recurrente. Resultado: [REVISAR] completar con porcentaje de cumplimiento de SLA, tickets perdidos antes/después, u horas mensuales de administración ahorradas en facturación.</t>
+    <t>MANAS-TI. Situación inicial: control impreciso de horas facturables, desvíos de tiempo en proyectos y administración desintegrada de la operación técnica. Qué se hizo: implementación de Odoo con Proyecto y Hojas de Horas como núcleo, conectando la ejecución técnica con la facturación y la administración.</t>
+  </si>
+  <si>
+    <t>PLUS-IT SERVICIOS S.A.S. Situación inicial: SLA comprometidos pero no medidos, facturación de abonos recurrentes armada manualmente y tickets de soporte que se perdían entre canales. Qué se hizo: implementación de Odoo con Mesa de Ayuda y Suscripciones, unificando la entrada de tickets y automatizando la facturación recurrente.</t>
   </si>
   <si>
     <t>EL DESAFÍO
@@ -1863,10 +1845,7 @@
     <t>Bancos y cobranzas. Conciliación bancaria y gestión de cuenta corriente de clientes industriales, con plazos de pago largos.</t>
   </si>
   <si>
-    <t>NP ELECTRÓNICA INDUSTRIAL. Situación inicial: trazabilidad de garantías ineficiente, dificultad para controlar micro-componentes y obsolescencia, y seguimiento de reparaciones en papel. Qué se hizo: implementación de Odoo con el módulo de Reparación y trazabilidad por número de serie, conectando el taller con el stock de componentes y con la facturación. Resultado: [REVISAR] completar con tiempo promedio de reparación, reclamos de garantía resueltos sin conflicto, o valor de stock obsoleto identificado.</t>
-  </si>
-  <si>
-    <t>[REVISAR] Podría cubrirse con Imoberdoff, que comparte el problema de taller y repuestos aunque esté en otro agrupador. Decisión de Eynes según cómo se navegue el sitio.</t>
+    <t>NP ELECTRÓNICA INDUSTRIAL. Situación inicial: trazabilidad de garantías ineficiente, dificultad para controlar micro-componentes y obsolescencia, y seguimiento de reparaciones en papel. Qué se hizo: implementación de Odoo con el módulo de Reparación y trazabilidad por número de serie, conectando el taller con el stock de componentes y con la facturación.</t>
   </si>
   <si>
     <t>EL DESAFÍO
@@ -2775,1111 +2754,1084 @@
       <c r="J11" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="K11" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>192</v>
-      </c>
     </row>
     <row r="12" ht="21.75" customHeight="1">
       <c r="A12" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>162</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="M12" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="N12" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="O12" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="J12" s="1" t="s">
+      <c r="P12" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="R12" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="S12" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="13" ht="27.0" customHeight="1">
       <c r="A13" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>162</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="K13" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="M13" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="N13" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="O13" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="J13" s="1" t="s">
+      <c r="P13" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="Q13" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="R13" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="S13" s="1" t="s">
         <v>221</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="14" ht="24.0" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>162</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="M14" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="N14" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="O14" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="P14" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="Q14" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="R14" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="S14" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="15" ht="30.0" customHeight="1">
       <c r="A15" s="2" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>162</v>
       </c>
       <c r="D15" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="M15" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="N15" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="O15" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="P15" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="Q15" s="1" t="s">
         <v>160</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" ht="29.25" customHeight="1">
       <c r="A16" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="K16" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="M16" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="N16" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="P16" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="J16" s="1" t="s">
+      <c r="R16" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="S16" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="17" ht="28.5" customHeight="1">
       <c r="A17" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="K17" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="P17" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="R17" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="S17" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="18" ht="33.75" customHeight="1">
       <c r="A18" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="D18" s="1" t="s">
+      <c r="J18" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="K18" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="M18" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="N18" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="O18" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="J18" s="1" t="s">
+      <c r="P18" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="R18" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="S18" s="1" t="s">
         <v>303</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="19" ht="23.25" customHeight="1">
       <c r="A19" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="K19" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="M19" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="N19" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="P19" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="J19" s="1" t="s">
+      <c r="R19" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="S19" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="20" ht="27.75" customHeight="1">
       <c r="A20" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="I20" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="D20" s="1" t="s">
+      <c r="J20" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="K20" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="M20" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="N20" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="O20" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="P20" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="Q20" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="R20" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="S20" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="21" ht="21.75" customHeight="1">
       <c r="A21" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="D21" s="1" t="s">
+      <c r="J21" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="K21" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="M21" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="N21" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="O21" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="P21" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="Q21" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="R21" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="S21" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>356</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>341</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="22" ht="26.25" customHeight="1">
       <c r="A22" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="D22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="M22" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="N22" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="O22" s="1" t="s">
         <v>369</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="P22" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="Q22" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="R22" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="S22" s="1" t="s">
         <v>373</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>375</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>376</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>377</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="D23" s="1" t="s">
+      <c r="J23" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="K23" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="L23" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="M23" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>389</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>390</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>391</v>
       </c>
       <c r="N23" s="1" t="s">
         <v>50</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="24" ht="21.75" customHeight="1">
       <c r="A24" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="J24" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="K24" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="M24" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="N24" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="O24" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="P24" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="R24" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="S24" s="1" t="s">
         <v>406</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>410</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="25" ht="25.5" customHeight="1">
       <c r="A25" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="D25" s="1" t="s">
+      <c r="J25" s="1" t="s">
         <v>415</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="K25" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="L25" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="M25" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="N25" s="1" t="s">
         <v>419</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="O25" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="P25" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="Q25" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="L25" s="1" t="s">
+      <c r="R25" s="1" t="s">
         <v>423</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="S25" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="26" ht="21.0" customHeight="1">
       <c r="A26" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="D26" s="1" t="s">
+      <c r="J26" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="L26" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="M26" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="N26" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="O26" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="J26" s="1" t="s">
+      <c r="P26" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="R26" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="S26" s="1" t="s">
         <v>440</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="27" ht="23.25" customHeight="1">
       <c r="A27" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>447</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="H27" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>449</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="J27" s="1" t="s">
         <v>450</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="K27" s="1" t="s">
         <v>451</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="L27" s="1" t="s">
         <v>452</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="M27" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="N27" s="1" t="s">
         <v>454</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="O27" s="1" t="s">
         <v>455</v>
       </c>
-      <c r="J27" s="1" t="s">
+      <c r="P27" s="1" t="s">
         <v>456</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="R27" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="L27" s="1" t="s">
+      <c r="S27" s="1" t="s">
         <v>458</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="P27" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="R27" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="28" ht="28.5" customHeight="1">
       <c r="A28" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="J28" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="K28" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="L28" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="M28" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="N28" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="O28" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="P28" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="Q28" s="1" t="s">
         <v>475</v>
       </c>
-      <c r="L28" s="1" t="s">
+      <c r="R28" s="1" t="s">
         <v>476</v>
       </c>
-      <c r="M28" s="1" t="s">
+      <c r="S28" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="P28" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="Q28" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="R28" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="S28" s="1" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="29" ht="27.75" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="E29" s="1" t="s">
+      <c r="J29" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="K29" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="L29" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="M29" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="N29" s="1" t="s">
         <v>472</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="O29" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="J29" s="1" t="s">
+      <c r="P29" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="Q29" s="1" t="s">
         <v>474</v>
       </c>
-      <c r="K29" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="M29" s="1" t="s">
+      <c r="R29" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="S29" s="1" t="s">
         <v>477</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="O29" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="P29" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="Q29" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="30" ht="27.75" customHeight="1">
       <c r="A30" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>488</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="D30" s="1" t="s">
+      <c r="J30" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="K30" s="1" t="s">
         <v>490</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="L30" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="M30" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="N30" s="1" t="s">
         <v>493</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="O30" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="J30" s="1" t="s">
+      <c r="P30" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="Q30" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="R30" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="S30" s="1" t="s">
         <v>497</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="O30" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>503</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>504</v>
       </c>
     </row>
   </sheetData>
